--- a/DEAI/WEEK 6/MachineLearning.xlsx
+++ b/DEAI/WEEK 6/MachineLearning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kyran\Desktop\Semester 4 Projects VSC\Roody repo\HHS-Pyhthon-Pipeline\DEAI\WEEK 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D879BB6-2465-4E11-9D9D-6215783146E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0024F2D4-7773-4381-AAA6-869D44BF32CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
   <si>
     <t>Gekozen features:</t>
   </si>
@@ -73,6 +73,12 @@
   </si>
   <si>
     <t>0.6721886124684764</t>
+  </si>
+  <si>
+    <t>max_iter= 4000, eta0=0.00005</t>
+  </si>
+  <si>
+    <t>0.6718840352990239</t>
   </si>
 </sst>
 </file>
@@ -126,6 +132,143 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>251461</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>53817</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Afbeelding 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E252566-509A-A57D-B52C-CB0DF106E334}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4130041" y="7620"/>
+          <a:ext cx="2850356" cy="2171700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>137696</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>344805</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Afbeelding 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DF59B3C-1D58-4F46-6F1A-B9F0E3A0D94C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4091940" y="2332256"/>
+          <a:ext cx="3179445" cy="2300704"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>20175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>128589</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Afbeelding 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDA982B6-5A25-ED26-19D1-7409B04FBAD4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4030980" y="4775055"/>
+          <a:ext cx="3276600" cy="2485854"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -391,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
@@ -493,7 +636,56 @@
         <v>15</v>
       </c>
     </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.52075636627093E+16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3.37733660872856E+16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/DEAI/WEEK 6/MachineLearning.xlsx
+++ b/DEAI/WEEK 6/MachineLearning.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kyran\Desktop\Semester 4 Projects VSC\Roody repo\HHS-Pyhthon-Pipeline\DEAI\WEEK 6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Documents\Developments\Softwares\Python\HHS_Study\DEAI\WEEK 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0024F2D4-7773-4381-AAA6-869D44BF32CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B6067C-2909-46FE-8B74-EA5AF5D4682F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15510" yWindow="0" windowWidth="13395" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="26">
   <si>
     <t>Gekozen features:</t>
   </si>
@@ -79,13 +79,37 @@
   </si>
   <si>
     <t>0.6718840352990239</t>
+  </si>
+  <si>
+    <t>Roody</t>
+  </si>
+  <si>
+    <t>Kyran</t>
+  </si>
+  <si>
+    <t>Year Built, Fulll Bath, House Style</t>
+  </si>
+  <si>
+    <t>Year Built, Lot Area, Neighborhod</t>
+  </si>
+  <si>
+    <t>Year Built, Bedroom AbvGround, Neighborhod</t>
+  </si>
+  <si>
+    <t>Full Bath</t>
+  </si>
+  <si>
+    <t>Year Built, Bedroom AbvGround, House Style</t>
+  </si>
+  <si>
+    <t>fit_intercept=True, positive=True</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,16 +117,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -110,16 +166,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -138,16 +237,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>251461</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>61886</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>94020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>53817</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:colOff>472550</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>109331</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -170,8 +269,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4130041" y="7620"/>
-          <a:ext cx="2850356" cy="2171700"/>
+          <a:off x="14075679" y="280141"/>
+          <a:ext cx="2863078" cy="2215914"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -182,16 +281,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>137696</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>79264</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>74438</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>344805</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:colOff>499719</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>54202</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -214,8 +313,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4091940" y="2332256"/>
-          <a:ext cx="3179445" cy="2300704"/>
+          <a:off x="14093057" y="2461162"/>
+          <a:ext cx="2872869" cy="2125626"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -226,16 +325,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>20175</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>112773</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>40508</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>128589</xdr:rowOff>
+      <xdr:colOff>543466</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>69</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -258,12 +357,130 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4030980" y="4775055"/>
-          <a:ext cx="3276600" cy="2485854"/>
+          <a:off x="14126566" y="4386974"/>
+          <a:ext cx="2883107" cy="2212600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>21142</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>31354</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3869866</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>338903</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{337EC4ED-6001-F080-8823-EE25C43C4064}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5179019" y="597462"/>
+          <a:ext cx="3836330" cy="13543705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>247</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>137634</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>137981</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>445183</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB40BABF-E684-470B-B299-3A67C9506F38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9120161" y="695996"/>
+          <a:ext cx="3805406" cy="13434532"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -534,157 +751,381 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="59.42578125" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="6"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="D2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D3" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="8" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="1">
+      <c r="B12" s="2">
         <v>2.51841644709139E+16</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="1">
+      <c r="B13" s="2">
         <v>3382493367037000</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="15" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="5"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>0</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="58.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="66" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="2"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="2"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="66.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="2"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="2"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="65.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>4</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B58" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="1">
+      <c r="B59" s="2">
         <v>2.52075636627093E+16</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="1">
+      <c r="B60" s="2">
         <v>3.37733660872856E+16</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>10</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B61" s="1" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DEAI/WEEK 6/MachineLearning.xlsx
+++ b/DEAI/WEEK 6/MachineLearning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kyran\Desktop\Semester 4 Projects VSC\Roody repo\HHS-Pyhthon-Pipeline\DEAI\WEEK 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0024F2D4-7773-4381-AAA6-869D44BF32CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE9D2AF-BDB2-4327-A076-EDD31907A92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -227,22 +227,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>144781</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>20175</xdr:rowOff>
+      <xdr:rowOff>7621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
+      <xdr:colOff>441403</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>128589</xdr:rowOff>
+      <xdr:rowOff>167640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Afbeelding 4">
+        <xdr:cNvPr id="6" name="Afbeelding 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDA982B6-5A25-ED26-19D1-7409B04FBAD4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57CF2259-7F0D-343B-A343-A9EDC3E76D15}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -258,8 +258,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4030980" y="4775055"/>
-          <a:ext cx="3276600" cy="2485854"/>
+          <a:off x="4023361" y="4762501"/>
+          <a:ext cx="3344622" cy="2537459"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
